--- a/product_selector_out/STM32F7x3 - diff.xlsx
+++ b/product_selector_out/STM32F7x3 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,13 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -541,7 +547,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -611,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="18">
@@ -1017,18 +1023,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>D/A Converters (12-bit) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1040,23 +1050,46 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32F723VC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E36"/>
+  <autoFilter ref="A18:E37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F7x3 - diff.xlsx
+++ b/product_selector_out/STM32F7x3 - diff.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>594</v>
+        <v>603</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>575</v>
+        <v>584</v>
       </c>
     </row>
     <row r="18">
